--- a/data/trans_orig/P1412-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2012</t>
+          <t>Población con diagnóstico de angina de pecho en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>16582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>694012</t>
+          <t>693843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>702529</t>
+          <t>702537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685144</t>
+          <t>684825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>694909</t>
+          <t>694889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1382950</t>
+          <t>1383937</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1396148</t>
+          <t>1396028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27547</t>
+          <t>26806</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995842</t>
+          <t>998171</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1013447</t>
+          <t>1013595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1014527</t>
+          <t>1014300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025219</t>
+          <t>1025434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2018191</t>
+          <t>2018932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2035825</t>
+          <t>2036508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747447</t>
+          <t>747313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756599</t>
+          <t>756605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760291</t>
+          <t>760414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773140</t>
+          <t>773112</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1513424</t>
+          <t>1512058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1528422</t>
+          <t>1528330</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935472</t>
+          <t>935535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945715</t>
+          <t>945716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1041342</t>
+          <t>1040019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1049893</t>
+          <t>1049871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1981204</t>
+          <t>1981971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1993673</t>
+          <t>1994574</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>34907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16551</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37435</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63667</t>
+          <t>64582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3391318</t>
+          <t>3391872</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3411825</t>
+          <t>3412764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3515533</t>
+          <t>3515915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3536417</t>
+          <t>3536864</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6916080</t>
+          <t>6915165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6945203</t>
+          <t>6944769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2016</t>
+          <t>Población con diagnóstico de angina de pecho en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665706</t>
+          <t>665660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673952</t>
+          <t>673728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663090</t>
+          <t>663673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671810</t>
+          <t>671817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1332913</t>
+          <t>1333669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1344562</t>
+          <t>1344538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>22934</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1003970</t>
+          <t>1004639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017416</t>
+          <t>1017689</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1032728</t>
+          <t>1032030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1041902</t>
+          <t>1041898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2042066</t>
+          <t>2042410</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2057677</t>
+          <t>2057632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>15976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,82 +3380,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4733</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11911</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>12637</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>6420</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>22288</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4733</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12019</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12637</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6305</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>22014</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743885</t>
+          <t>743576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756341</t>
+          <t>755787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,82 +3493,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>780278</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>773100</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>783744</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1531926</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1522275</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1538143</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>98,56%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>780278</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>772992</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>783746</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,84%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1421</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1531926</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1522549</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1538258</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14686</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>928009</t>
+          <t>927284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935914</t>
+          <t>935908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1029093</t>
+          <t>1028746</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1040605</t>
+          <t>1040603</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1961589</t>
+          <t>1960606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1974803</t>
+          <t>1975232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29579</t>
+          <t>30233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60229</t>
+          <t>60484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3355101</t>
+          <t>3357025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3377316</t>
+          <t>3377507</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3514963</t>
+          <t>3514309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3533449</t>
+          <t>3534000</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6878663</t>
+          <t>6878408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6905651</t>
+          <t>6905506</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de angina de pecho en 2023</t>
+          <t>Población con diagnóstico de angina de pecho en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>627317</t>
+          <t>626750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>633721</t>
+          <t>633751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665383</t>
+          <t>665743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671999</t>
+          <t>671916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1295914</t>
+          <t>1295969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1304395</t>
+          <t>1304478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1179010</t>
+          <t>1179397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1188848</t>
+          <t>1189040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>950307</t>
+          <t>949796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>956176</t>
+          <t>956157</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2133586</t>
+          <t>2133418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2144096</t>
+          <t>2143955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>684815</t>
+          <t>684588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>697387</t>
+          <t>697153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>925538</t>
+          <t>925888</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>931589</t>
+          <t>931537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1614518</t>
+          <t>1613723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1628661</t>
+          <t>1627827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19614</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>907217</t>
+          <t>908629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919987</t>
+          <t>920209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1079913</t>
+          <t>1079592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1087667</t>
+          <t>1087797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1991867</t>
+          <t>1991163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2006162</t>
+          <t>2005988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>25356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60742</t>
+          <t>60708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3413847</t>
+          <t>3412896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3434693</t>
+          <t>3434225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3630420</t>
+          <t>3630596</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3643400</t>
+          <t>3643542</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7050632</t>
+          <t>7050666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7075527</t>
+          <t>7075167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1412-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1412-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +782,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>9406</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>17001</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>9406</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>4491</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>16582</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>693843</t>
+          <t>693606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>702537</t>
+          <t>702393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>684825</t>
+          <t>685075</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>694889</t>
+          <t>694956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +895,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1391113</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1383518</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1396120</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,69%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1391113</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1383937</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1396028</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26806</t>
+          <t>26250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>998171</t>
+          <t>998011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1013595</t>
+          <t>1013384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1014300</t>
+          <t>1013228</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025434</t>
+          <t>1025561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2018932</t>
+          <t>2019488</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2036508</t>
+          <t>2037176</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16760</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747313</t>
+          <t>747562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756605</t>
+          <t>756600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760414</t>
+          <t>760980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773112</t>
+          <t>773069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1512058</t>
+          <t>1512813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1528330</t>
+          <t>1528455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935535</t>
+          <t>935656</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945716</t>
+          <t>945727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1040019</t>
+          <t>1041392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1049871</t>
+          <t>1049879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1981971</t>
+          <t>1980975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1994574</t>
+          <t>1994520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34907</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37053</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34978</t>
+          <t>35976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>65540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3391872</t>
+          <t>3392539</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3412764</t>
+          <t>3412587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3515915</t>
+          <t>3516221</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3536864</t>
+          <t>3536881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6915165</t>
+          <t>6914207</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6944769</t>
+          <t>6943771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665660</t>
+          <t>665748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673728</t>
+          <t>673752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663673</t>
+          <t>662660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671817</t>
+          <t>671815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1333669</t>
+          <t>1333148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1344538</t>
+          <t>1344565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>22773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1004639</t>
+          <t>1004368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017689</t>
+          <t>1017463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1032030</t>
+          <t>1033372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2042410</t>
+          <t>2042571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2057632</t>
+          <t>2058181</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,47 +3415,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>12637</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>23526</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12637</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6420</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>22288</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743576</t>
+          <t>743446</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>755787</t>
+          <t>756467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>773100</t>
+          <t>774035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>783744</t>
+          <t>783841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,47 +3528,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,85%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1421</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1531926</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1521037</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1537402</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>98,48%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,84%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1421</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1531926</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1522275</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1538143</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1659</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,47 +3758,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>11931</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>19853</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>11931</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>6114</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>20740</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>927284</t>
+          <t>927434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935908</t>
+          <t>935804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1028746</t>
+          <t>1028927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1040603</t>
+          <t>1040559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,47 +3871,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1879</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1969415</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1961493</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1975365</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,7%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1879</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1969415</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1960606</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1975232</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37325</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>31245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60484</t>
+          <t>59836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3357025</t>
+          <t>3356275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3377507</t>
+          <t>3377392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3514309</t>
+          <t>3513863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3534000</t>
+          <t>3533417</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6878408</t>
+          <t>6879056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6905506</t>
+          <t>6907647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>631413</t>
+          <t>686544</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>626750</t>
+          <t>682500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>633751</t>
+          <t>688890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>669638</t>
+          <t>726716</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665743</t>
+          <t>723000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>671916</t>
+          <t>729206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1301052</t>
+          <t>1413259</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1295969</t>
+          <t>1408036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1304478</t>
+          <t>1416984</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674683</t>
+          <t>732011</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674683</t>
+          <t>732011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674683</t>
+          <t>732011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310125</t>
+          <t>1422721</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310125</t>
+          <t>1422721</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310125</t>
+          <t>1422721</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,27 +4999,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1185404</t>
+          <t>1041131</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1179397</t>
+          <t>1035404</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1189040</t>
+          <t>1044338</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,22 +5112,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>954236</t>
+          <t>1066087</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>949796</t>
+          <t>1061585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>956157</t>
+          <t>1068307</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2139639</t>
+          <t>2107218</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2133418</t>
+          <t>2100766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2143955</t>
+          <t>2111478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191543</t>
+          <t>1047519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957437</t>
+          <t>1070187</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148980</t>
+          <t>2117706</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148980</t>
+          <t>2117706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148980</t>
+          <t>2117706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20199</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>693015</t>
+          <t>790269</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>684588</t>
+          <t>780737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>697153</t>
+          <t>795229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>929694</t>
+          <t>806902</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>925888</t>
+          <t>802391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>931537</t>
+          <t>808879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1622709</t>
+          <t>1597171</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1613723</t>
+          <t>1588490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1627827</t>
+          <t>1603158</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701607</t>
+          <t>799862</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701607</t>
+          <t>799862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701607</t>
+          <t>799862</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932315</t>
+          <t>810145</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932315</t>
+          <t>810145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932315</t>
+          <t>810145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633922</t>
+          <t>1610007</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633922</t>
+          <t>1610007</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633922</t>
+          <t>1610007</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,22 +5650,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11393</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18202</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>14454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>29553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -5763,27 +5763,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>915438</t>
+          <t>977538</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>908629</t>
+          <t>970728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920209</t>
+          <t>983072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1084453</t>
+          <t>1108900</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1079592</t>
+          <t>1103136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1087797</t>
+          <t>1112327</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1999891</t>
+          <t>2086438</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1991163</t>
+          <t>2077742</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2005988</t>
+          <t>2092841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091516</t>
+          <t>1117233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018347</t>
+          <t>2107295</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018347</t>
+          <t>2107295</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018347</t>
+          <t>2107295</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42526</t>
+          <t>45421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12410</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25356</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>42561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>67365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3425269</t>
+          <t>3495481</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3412896</t>
+          <t>3482731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3434225</t>
+          <t>3504176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3638022</t>
+          <t>3708605</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3630596</t>
+          <t>3701428</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3643542</t>
+          <t>3714849</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7063291</t>
+          <t>7204086</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7050666</t>
+          <t>7190364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7075167</t>
+          <t>7215168</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3455422</t>
+          <t>3528152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655952</t>
+          <t>3729577</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111374</t>
+          <t>7257729</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
